--- a/reports/pdf_change_20260917.xlsx
+++ b/reports/pdf_change_20260917.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,551억   ·   현금 34억(0.7%)      당일 2026-09-17  vs  전영업일 2026-09-16      매수 5종목  /  매도 7종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,551억      당일 2026-09-17  vs  전영업일 2026-09-16      매수 5종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -772,23 +772,23 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1364413677</v>
+        <v>-1122371766</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.30%</t>
+          <t>0.77%→0.47%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>78→39</t>
+          <t>112→73</t>
         </is>
       </c>
     </row>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1122371766</v>
+        <v>-1364413677</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.47%</t>
+          <t>0.59%→0.30%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>112→73</t>
+          <t>78→39</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,351억   ·   현금 43억(1.3%)      당일 2026-09-17  vs  전영업일 2026-09-16      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,351억      당일 2026-09-17  vs  전영업일 2026-09-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -963,7 +963,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,529억   ·   현금 38억(1.5%)      당일 2026-09-17  vs  전영업일 2026-09-16      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,529억      당일 2026-09-17  vs  전영업일 2026-09-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -987,7 +987,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,921억   ·   현금 13억(0.7%)      당일 2026-09-17  vs  전영업일 2026-09-16      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,921억      당일 2026-09-17  vs  전영업일 2026-09-16      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 279억   ·   현금 2억(0.5%)      당일 2026-09-17  vs  전영업일 2026-09-16      매수 4종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 279억      당일 2026-09-17  vs  전영업일 2026-09-16      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1501,7 +1501,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 477억   ·   현금 4억(0.9%)      당일 2026-09-17  vs  전영업일 2026-09-16      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 477억      당일 2026-09-17  vs  전영업일 2026-09-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>

--- a/reports/pdf_change_20260917.xlsx
+++ b/reports/pdf_change_20260917.xlsx
@@ -772,23 +772,23 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1122371766</v>
+        <v>-1364413677</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.47%</t>
+          <t>0.59%→0.30%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>112→73</t>
+          <t>78→39</t>
         </is>
       </c>
     </row>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1364413677</v>
+        <v>-1122371766</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.30%</t>
+          <t>0.77%→0.47%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>78→39</t>
+          <t>112→73</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260917.xlsx
+++ b/reports/pdf_change_20260917.xlsx
@@ -772,23 +772,23 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1364413677</v>
+        <v>-1122371766</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.30%</t>
+          <t>0.77%→0.47%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>78→39</t>
+          <t>112→73</t>
         </is>
       </c>
     </row>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1122371766</v>
+        <v>-1364413677</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.47%</t>
+          <t>0.59%→0.30%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>112→73</t>
+          <t>78→39</t>
         </is>
       </c>
     </row>
